--- a/OSBAMS_Pi_Power_Interposer_RevA_RC2/bom/OSBAMS_Pi_Power_Interposer_RevA_RC2_BOM.xlsx
+++ b/OSBAMS_Pi_Power_Interposer_RevA_RC2/bom/OSBAMS_Pi_Power_Interposer_RevA_RC2_BOM.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Samtec SSW-120-01-S-D: 2x20, 2.54 mm, through-hole vertical receptacle, 30 uin gold / tin tails, body 8.51 mm, tail 2.64 mm, 4.7 A (one pin powered per row). Mounted from the UNDERSIDE, soldered from the top.</t>
+          <t>Samtec SSW-120-01-L-D: 2x20, 2.54 mm, through-hole vertical receptacle, 10 uin gold mating / tin tails, body 8.51 mm, tail 2.64 mm, 4.7 A (one pin powered per row). Mounted from the UNDERSIDE, soldered from the top.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>SSW-120-01-S-D</t>
+          <t>SSW-120-01-L-D</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>OSBAMS_PiPwr:SSW-120-01-S-D_RPi_TopView (pad pattern by Pi pin number, 1.0 mm drill - confirm vs Samtec footprint)</t>
+          <t>OSBAMS_PiPwr:SSW-120-01-L-D_RPi_TopView (pad pattern by Pi pin number, 1.0 mm drill - confirm vs Samtec footprint)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Dimensions CONFIRMED by Samtec catalog F-226 (8.51 mm body, lead style -01 = 2.64 mm tail). PLATING LETTER OPEN: catalog plating codes are -F/-L (10 uin Au)/-G (20 uin Au)/-T; -S is a row option there. Confirm the orderable code (owner: SSW-120-01-S-D) with the distributor, or order SSW-120-01-L-D / -G-D. Do NOT use SSW-120-04-G-D (14.83 mm tail, no stock)</t>
+          <t>Exact orderable MPN (user-relayed from the Samtec page; 10 uin Au mating, tin post, 4.7 A per contact with 2 pins powered). Dimensions CONFIRMED by Samtec catalog F-226 (8.51 mm body, lead style -01 = 2.64 mm tail). Do NOT use SSW-120-04-G-D (14.83 mm tail, no stock)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Micro-Fit receptacle housing 43025-0400 at both ends, 4 x 16 AWG &lt;= 150 mm, crimped (off-board; see the power-board BOM/Harness.md)</t>
+          <t>Micro-Fit receptacle housing 43025-0400 at both ends, 4 x 18 AWG &lt;= 150 mm, crimped (off-board; see the power-board BOM/Harness.md)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -636,13 +636,13 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43025-0400 + 43030-family terminals (owner selects exact MPN)</t>
+          <t>43025-0400 + 43030-0038 terminals</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Terminals and wire NOT verified (no Molex 43030 drawing in the project); strain relief required</t>
+          <t>18 AWG UL1061-type wire (insulation OD &lt;= 1.85 mm); terminal verified from Molex ATS-638280200; strain relief required</t>
         </is>
       </c>
     </row>
